--- a/resources/Z517/Z517_codebaseline.xlsx
+++ b/resources/Z517/Z517_codebaseline.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,11 +699,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S向边缘Mura</t>
+          <t>S向群亮线</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6e-05</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>34056</v>
@@ -722,11 +722,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>单亮点</t>
+          <t>S向群暗线</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.00109</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>34056</v>
@@ -745,11 +745,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>右斜黑色带状Mura</t>
+          <t>S向边缘Mura</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3e-05</v>
+        <v>6e-05</v>
       </c>
       <c r="E14" t="n">
         <v>34056</v>
@@ -768,11 +768,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>大圆环Mura</t>
+          <t>单亮点</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3e-05</v>
+        <v>0.00109</v>
       </c>
       <c r="E15" t="n">
         <v>34056</v>
@@ -791,11 +791,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>大面积亮点</t>
+          <t>右斜黑色带状Mura</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.00012</v>
+        <v>3e-05</v>
       </c>
       <c r="E16" t="n">
         <v>34056</v>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>大面积片状彩斑Mura</t>
+          <t>大圆环Mura</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -837,11 +837,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>孔区S向分屏</t>
+          <t>大面积亮点</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3e-05</v>
+        <v>0.00012</v>
       </c>
       <c r="E18" t="n">
         <v>34056</v>
@@ -860,11 +860,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>常亮白斑</t>
+          <t>大面积片状彩斑Mura</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.00038</v>
+        <v>3e-05</v>
       </c>
       <c r="E19" t="n">
         <v>34056</v>
@@ -883,11 +883,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>常暗黑斑Mura</t>
+          <t>孔区S向分屏</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.00159</v>
+        <v>3e-05</v>
       </c>
       <c r="E20" t="n">
         <v>34056</v>
@@ -906,11 +906,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>彩斑Mura</t>
+          <t>常亮白斑</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.00079</v>
+        <v>0.00038</v>
       </c>
       <c r="E21" t="n">
         <v>34056</v>
@@ -929,11 +929,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>微亮点</t>
+          <t>常暗黑斑Mura</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.00012</v>
+        <v>0.00159</v>
       </c>
       <c r="E22" t="n">
         <v>34056</v>
@@ -952,11 +952,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>斑中带点</t>
+          <t>彩斑Mura</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3e-05</v>
+        <v>0.00079</v>
       </c>
       <c r="E23" t="n">
         <v>34056</v>
@@ -975,11 +975,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>暗点</t>
+          <t>微亮点</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.00476</v>
+        <v>0.00012</v>
       </c>
       <c r="E24" t="n">
         <v>34056</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>流星状划线</t>
+          <t>斑中带点</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>灰阶点状白斑Mura</t>
+          <t>暗点</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3e-05</v>
+        <v>0.00476</v>
       </c>
       <c r="E26" t="n">
         <v>34056</v>
@@ -1044,11 +1044,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>白画面黑斑Mura</t>
+          <t>流星状划线</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.001</v>
+        <v>3e-05</v>
       </c>
       <c r="E27" t="n">
         <v>34056</v>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>群亮点</t>
+          <t>灰阶点状白斑Mura</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.00117</v>
+        <v>3e-05</v>
       </c>
       <c r="E28" t="n">
         <v>34056</v>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>群暗点</t>
+          <t>白画面黑斑Mura</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.00373</v>
+        <v>0.001</v>
       </c>
       <c r="E29" t="n">
         <v>34056</v>
@@ -1113,13 +1113,59 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>群亮点</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.00117</v>
+      </c>
+      <c r="E30" t="n">
+        <v>34056</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>群暗点</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.00373</v>
+      </c>
+      <c r="E31" t="n">
+        <v>34056</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>雪花状Mura</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D32" t="n">
         <v>3e-05</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E32" t="n">
         <v>34056</v>
       </c>
     </row>
@@ -1169,7 +1215,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T09:36:04.967569</t>
+          <t>2026-08-11T11:23:54.411462</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1239,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>missing_file</t>
+          <t>missing_period_rows</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1263,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1275,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
     </row>
